--- a/reference/origins/product info/Pre-roll pt2 Product List Final for WA.xlsx
+++ b/reference/origins/product info/Pre-roll pt2 Product List Final for WA.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-Roll Products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seed Data Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pre-Roll Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Seed Data Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -656,7 +656,7 @@
       </c>
       <c r="N3" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Linalool</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="L6" s="14" t="inlineStr">
         <is>
+          <t>Caryophyllene</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
           <t>Limonene</t>
-        </is>
-      </c>
-      <c r="M6" s="14" t="inlineStr">
-        <is>
-          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="N6" s="14" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Linalool</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="N12" s="14" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="M13" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Ocimene</t>
         </is>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
-          <t>Pinene</t>
+          <t>Myrcene</t>
         </is>
       </c>
     </row>
@@ -1350,17 +1350,17 @@
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Myrcene</t>
         </is>
       </c>
       <c r="N14" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="N16" s="14" t="inlineStr">
         <is>
-          <t>Pinene</t>
+          <t>Limonene</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="N21" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Linalool</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="N23" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Linalool</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="N24" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Linalool</t>
         </is>
       </c>
     </row>
@@ -2158,12 +2158,12 @@
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="N26" s="14" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Terpinolene</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Myrcene</t>
         </is>
       </c>
     </row>
@@ -2750,12 +2750,12 @@
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Humulene</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Myrcene</t>
         </is>
       </c>
       <c r="N35" s="14" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Humulene</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Myrcene</t>
         </is>
       </c>
       <c r="N36" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Pinene</t>
         </is>
       </c>
     </row>
@@ -3534,17 +3534,17 @@
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="N47" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Myrcene</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Myrcene</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="L51" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="M51" s="14" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="N51" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Myrcene</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="N53" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Pinene</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="N56" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Linalool</t>
         </is>
       </c>
     </row>
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L57" s="14" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="M57" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="N57" s="14" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="N58" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Myrcene</t>
         </is>
       </c>
     </row>
@@ -4458,17 +4458,17 @@
       </c>
       <c r="L61" s="14" t="inlineStr">
         <is>
-          <t>Myrcene</t>
+          <t>Caryophyllene</t>
         </is>
       </c>
       <c r="M61" s="14" t="inlineStr">
         <is>
-          <t>Caryophyllene</t>
+          <t>Limonene</t>
         </is>
       </c>
       <c r="N61" s="14" t="inlineStr">
         <is>
-          <t>Limonene</t>
+          <t>Myrcene</t>
         </is>
       </c>
     </row>
